--- a/data_extactor/batch_10_fa/trimmed/batch_0089_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0089_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استواری دست و بازو | مرتب‌سازی اطلاعات | چابکی دستی | دید نزدیک | هماهنگی اندام‌ها | دقت کنترل | چابکی انگشتان</t>
+          <t>ثبات دست و بازو | ترتیب‌دهی اطلاعات | مهارت دستی | بینایی نزدیک | هماهنگی چند عضو | دقت کنترل | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>برشکاران و پیراستاران دستی | تنظیم‌کنندگان، اپراتورها و مراقبان دستگاه‌های برش و ورقه‌کنی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات تولید مصنوعات کاغذی | چرخکاران و دوزندگان صنعتی | اپراتورها و مراقبان ماشین‌آلات کفاشی</t>
+          <t>برشکاران و پیرایشگران دستی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌آلات کفش</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال</t>
+          <t>نظارت | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>استواری دست و بازو | چابکی انگشتان | دقت کنترل | هماهنگی اندام‌ها | چابکی دستی | دید نزدیک | حساسیت به مسئله</t>
+          <t>ثبات دست و بازو | مهارت انگشتان | دقت کنترل | هماهنگی چند عضو | مهارت دستی | بینایی نزدیک | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و مراقبان دستگاه‌های برش و ورقه‌کنی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | چرخکاران و دوزندگان صنعتی | اپراتورها و مراقبان ماشین‌های رنگرزی و سفیدگری منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف</t>
+          <t>تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | تفکر انتقادی | شنیدن فعال</t>
+          <t>سخن گفتن | نظارت | تفکر انتقادی | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | مدیریت و امور اداری | مکانیک | ایمنی و امنیت عمومی</t>
+          <t>تولید و فرآوری | مدیریت و اداره | مکانیک | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استواری دست و بازو | دقت کنترل | چابکی انگشتان | چابکی دستی | زمان واکنش | هماهنگی اندام‌ها | دید نزدیک</t>
+          <t>ثبات دست و بازو | دقت کنترل | مهارت انگشتان | مهارت دستی | زمان عکس‌العمل | هماهنگی چند عضو | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران کلاف | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | چرخکاران و دوزندگان صنعتی | اپراتورها و مراقبان ماشین‌های رنگرزی و سفیدگری منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بافندگی و تریکوبافی</t>
+          <t>سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | چرخکاران صنعتی | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بافندگی و تریکوبافی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | زبان انگلیسی | ریاضیات | آموزش و یاددهی | مکانیک</t>
+          <t>تولید و فرآوری | زبان انگلیسی | ریاضیات | آموزش و پرورش | مکانیک</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دقت کنترل | دید نزدیک | چابکی انگشتان | استواری دست و بازو | چابکی دستی | کنترل نرخ</t>
+          <t>حساسیت به مسئله | دقت کنترل | بینایی نزدیک | مهارت انگشتان | ثبات دست و بازو | مهارت دستی | کنترل نرخ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | اپراتورها و مراقبان ماشین‌های رنگرزی و سفیدگری منسوجات | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف</t>
+          <t>تنظیم‌کنندگان و اپراتورهای ماشین‌های اکستروژن و کشش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | مکانیک‌های ماشین‌آلات صنعتی | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های قالب‌گیری، ماهیچه‌سازی و ریخته‌گری فلز و پلاستیک | اپراتورها و متصدیان ماشین‌های سفیدگری و رنگرزی نساجی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>طراحی | ریاضیات | زبان انگلیسی | تولید و فرآوری | آموزش و یاددهی</t>
+          <t>طراحی | ریاضیات | زبان انگلیسی | تولید و فرآوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>تجسم فضایی | دید نزدیک | ابتکار و اصالت | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال ریاضی | چابکی انگشتان</t>
+          <t>تجسم | بینایی نزدیک | اصالت | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال ریاضی | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>برشکاران و پیراستاران دستی | طراحان مد و لباس | الگوسازان فلز و پلاستیک | دوزندگان دستی | چرخکاران و دوزندگان صنعتی | خیاطان، دوزندگان زنانه و سفارشی‌دوزان | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات</t>
+          <t>برشکاران و پیرایشگران دستی | طراحان مد و پوشاک | الگوسازان فلز و پلاستیک | دوزندگان دستی | چرخکاران صنعتی | خیاطان و دوزندگان سفارشی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>استواری دست و بازو | چابکی دستی | چابکی انگشتان | دید نزدیک | دقت کنترل | هماهنگی اندام‌ها | تجسم فضایی</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | دقت کنترل | هماهنگی چند عضو | تجسم</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>صافکاران و تعمیرکاران بدنه خودرو | کابینت‌سازان و نجاران کارگاهی | برشکاران و پیراستاران دستی | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | دوزندگان دستی | چرخکاران و دوزندگان صنعتی | کارگران و تعمیرکاران کفش و چرم</t>
+          <t>صافکار و نقاش خودرو | کابینت‌سازان و نجاران کارگاهی | برشکاران و پیرایشگران دستی | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | دوزندگان دستی | چرخکاران صنعتی | کارگران و تعمیرکاران کفش و چرم</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | طراحی | مکانیک | زبان انگلیسی | ریاضیات | خدمات مشتریان و خدمات فردی | شیمی</t>
+          <t>تولید و فرآوری | طراحی | مکانیک | زبان انگلیسی | ریاضیات | خدمات مشتری و شخصی | شیمی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | استواری دست و بازو | هماهنگی اندام‌ها | دقت کنترل | قدرت ایستا | دید نزدیک</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>چرخکاران و دوزندگان صنعتی | دوزندگان دستی | خیاطان، دوزندگان زنانه و سفارشی‌دوزان | رویه‌کوبان و مبل‌کوبان | کارگران و تعمیرکاران کفش و چرم | اتوکاران و پرس‌کاران منسوجات و پوشاک | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات</t>
+          <t>چرخکاران صنعتی | دوزندگان دستی | خیاطان و دوزندگان سفارشی | رویه‌کوبان و مبل‌کوبان | کارگران و تعمیرکاران کفش و چرم | اتوکاران منسوجات، پوشاک و مواد وابسته | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های برش منسوجات</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | نرم‌افزار برآورد و متره رایانه‌ای | سیستم مدیریت نگهداری و تعمیرات رایانه‌ای CMMS | Microsoft Excel | Microsoft Outlook | Microsoft Windows</t>
+          <t>Autodesk AutoCAD | نرم‌افزار برآورد و متره رایانه‌ای | سیستم مدیریت نگهداری کامپیوتری CMMS | Microsoft Excel | Microsoft Outlook | Microsoft Windows</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استواری دست و بازو | چابکی دستی | چابکی انگشتان | دید نزدیک | دقت کنترل | هماهنگی اندام‌ها | تجسم فضایی</t>
+          <t>ثبات دست و بازو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | دقت کنترل | هماهنگی چند عضو | تجسم</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>نجاران عمومی | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | کارگران کمکی نجاران | مدل‌سازان چوب | الگوسازان چوب | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اره‌کشی چوب | رویه‌کوبان و مبل‌کوبان</t>
+          <t>نجاران و درودگران | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | کمک‌نجاران | مدل‌سازان چوب | الگوسازان چوب | تنظیم‌کنندگان، متصدیان و اپراتورهای اره‌ چوب‌بری | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | سخن گفتن</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>دید نزدیک | تشخیص رنگ | استواری دست و بازو | چابکی دستی | دقت کنترل | تجسم فضایی | چابکی انگشتان</t>
+          <t>بینایی نزدیک | تشخیص رنگ بصری | ثبات دست و بازو | مهارت دستی | دقت کنترل | تجسم | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و نجاران کارگاهی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های پوشش‌دهی، رنگ‌آمیزی و پاشش | سنباده‌زنان و پرداخت‌کاران پارکت و کف چوبی | کارگران سنگ‌زنی و پرداخت‌کاری دستی | نقاشان ساختمان و تاسیسات | کارگران رنگ‌آمیزی، پوشش‌دهی و تزیین | رویه‌کوبان و مبل‌کوبان</t>
+          <t>کابینت‌سازان و نجاران کارگاهی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های پوشش‌دهی، رنگ‌کاری و اسپری | ساب‌زنان و پرداخت‌کاران کف | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | نقاشان ساختمان و تاسیسات | کارگران رنگ‌کاری، پوشش‌دهی و تزیین قطعات | رویه‌کوبان و مبل‌کوبان</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>تولید و فرآوری | طراحی | ساختمان و ساخت‌وساز | مهندسی و فناوری | ریاضیات | مدیریت و امور اداری | مکانیک</t>
+          <t>تولید و فرآوری | طراحی | ساختمان و ساخت‌وساز | مهندسی و فناوری | ریاضیات | مدیریت و اداره | مکانیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>دید نزدیک | استواری دست و بازو | چابکی انگشتان | دقت کنترل | چابکی دستی | تجسم فضایی | مرتب‌سازی اطلاعات</t>
+          <t>بینایی نزدیک | ثبات دست و بازو | مهارت انگشتان | دقت کنترل | مهارت دستی | تجسم | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>کابینت‌سازان و نجاران کارگاهی | نجاران عمومی | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | مدل‌سازان فلز و پلاستیک | الگوسازان فلز و پلاستیک | الگوسازان چوب | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌آلات صنایع چوب به‌جز اره‌کشی</t>
+          <t>کابینت‌سازان و نجاران کارگاهی | نجاران و درودگران | پرداخت‌کاران و رنگ‌کاران چوب و مبلمان | مدل‌سازان فلز و پلاستیک | الگوسازان فلز و پلاستیک | الگوسازان چوب | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
